--- a/output/pdf_financials_xlsx/CN.xlsx
+++ b/output/pdf_financials_xlsx/CN.xlsx
@@ -7823,46 +7823,46 @@
         <v>1.896081</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>1.159885</v>
+        <v>0.948379</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>0</v>
+        <v>-0.30323</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>0</v>
+        <v>-0.09903099999999999</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>0</v>
+        <v>1.105494</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>0</v>
+        <v>-0.367553</v>
       </c>
       <c r="K118" s="3" t="n">
-        <v>0</v>
+        <v>-0.487954</v>
       </c>
       <c r="L118" s="3" t="n">
-        <v>0</v>
+        <v>-0.607249</v>
       </c>
       <c r="M118" s="3" t="n">
-        <v>0</v>
+        <v>-0.635733</v>
       </c>
       <c r="N118" s="3" t="n">
-        <v>0</v>
+        <v>-0.797399</v>
       </c>
       <c r="O118" s="3" t="n">
-        <v>0</v>
+        <v>-0.741729</v>
       </c>
       <c r="P118" s="3" t="n">
-        <v>0.389608</v>
+        <v>-0.507394</v>
       </c>
       <c r="Q118" s="3" t="n">
-        <v>0.030469</v>
+        <v>-2.204825</v>
       </c>
       <c r="R118" s="3" t="n">
-        <v>0.712743</v>
+        <v>-0.552743</v>
       </c>
       <c r="S118" s="3" t="n">
-        <v>0</v>
+        <v>-0.858588</v>
       </c>
     </row>
     <row r="119">
@@ -21360,7 +21360,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr"/>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E120" t="inlineStr">
         <is>
           <t>-</t>
@@ -25944,7 +25948,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D166" t="inlineStr"/>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E166" t="inlineStr">
         <is>
           <t>-</t>
@@ -29388,7 +29396,11 @@
           <t>Write-off of exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D199" t="inlineStr"/>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E199" t="inlineStr">
         <is>
           <t>-</t>
@@ -30326,7 +30338,11 @@
           <t>Write‐off of exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D208" t="inlineStr"/>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E208" t="inlineStr">
         <is>
           <t>-</t>
@@ -31480,7 +31496,11 @@
           <t>Write‐off of exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D219" t="inlineStr"/>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E219" t="inlineStr">
         <is>
           <t>-</t>
@@ -31796,7 +31816,11 @@
           <t>Exploration and evalution expenditures</t>
         </is>
       </c>
-      <c r="D222" t="inlineStr"/>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E222" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/CN.xlsx
+++ b/output/pdf_financials_xlsx/CN.xlsx
@@ -1059,25 +1059,25 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.103304</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.014735</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.029583</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.047069</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.017742</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.004654</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.003171</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>0</v>
@@ -1086,31 +1086,31 @@
         <v>0</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.004587</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.00107</v>
       </c>
       <c r="M12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.00319</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.00053</v>
       </c>
       <c r="P12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.044542</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>0.029404</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>0</v>
+        <v>6.9e-05</v>
       </c>
     </row>
     <row r="13">
@@ -2136,25 +2136,25 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-2.050533</v>
+        <v>-2.153837</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-1.058121</v>
+        <v>-1.072856</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.529486</v>
+        <v>-1.559069</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-6.229865</v>
+        <v>-6.276934</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-3.516307</v>
+        <v>-3.534049</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.834882</v>
+        <v>-0.8395359999999999</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.946384</v>
+        <v>-0.949555</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>-1.628973</v>
@@ -2163,31 +2163,31 @@
         <v>-0.246942</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-0.750636</v>
+        <v>-0.755223</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-0.437765</v>
+        <v>-0.438835</v>
       </c>
       <c r="M27" s="3" t="n">
         <v>-0.121161</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>2.33413</v>
+        <v>2.33094</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>0.119528</v>
+        <v>0.118998</v>
       </c>
       <c r="P27" s="3" t="n">
         <v>0.439405</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>1.22349</v>
+        <v>1.178948</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-4.735819</v>
+        <v>-4.765223</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>-1.474127</v>
+        <v>-1.474196</v>
       </c>
     </row>
     <row r="28">
@@ -2258,25 +2258,25 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-2.050533</v>
+        <v>-2.153837</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-1.058121</v>
+        <v>-1.072856</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.529486</v>
+        <v>-1.559069</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-6.229865</v>
+        <v>-6.276934</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-3.516307</v>
+        <v>-3.534049</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.834882</v>
+        <v>-0.8395359999999999</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.946384</v>
+        <v>-0.949555</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>-1.628973</v>
@@ -2285,31 +2285,31 @@
         <v>-0.246942</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-0.750636</v>
+        <v>-0.755223</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-0.437765</v>
+        <v>-0.438835</v>
       </c>
       <c r="M29" s="3" t="n">
         <v>-0.121161</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>2.33413</v>
+        <v>2.33094</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>0.119528</v>
+        <v>0.118998</v>
       </c>
       <c r="P29" s="3" t="n">
         <v>0.439405</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>1.22349</v>
+        <v>1.178948</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-4.735819</v>
+        <v>-4.765223</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>-1.474127</v>
+        <v>-1.474196</v>
       </c>
     </row>
     <row r="30">
@@ -2581,10 +2581,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>1.402437</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>4.027144</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>4.027144</v>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>1.402437</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.0195</v>
+        <v>4.046644</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>4.046644</v>
@@ -3435,10 +3435,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>1.435624</v>
+        <v>0.033187</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>4.062408</v>
+        <v>0.035264</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>0</v>
@@ -18488,7 +18488,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E92" s="5" t="n">
@@ -38024,7 +38024,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
@@ -42538,7 +42538,7 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
@@ -43070,7 +43070,7 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
@@ -46760,7 +46760,7 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E367" t="inlineStr">
@@ -49490,7 +49490,7 @@
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E393" s="5" t="n">

--- a/output/pdf_financials_xlsx/CN.xlsx
+++ b/output/pdf_financials_xlsx/CN.xlsx
@@ -7615,7 +7615,7 @@
         <v>0</v>
       </c>
       <c r="R114" s="3" t="n">
-        <v>0</v>
+        <v>-0.068815</v>
       </c>
       <c r="S114" s="3" t="n">
         <v>0</v>
@@ -21656,7 +21656,11 @@
           <t>Purchase of marketable securities</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr"/>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E123" t="inlineStr">
         <is>
           <t>-</t>
